--- a/Printer/Grading/2 stage/6-examples/Printer_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Printer/Grading/2 stage/6-examples/Printer_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20840" yWindow="-18760" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="printer" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="printer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>GPT-5 Generation</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to Off</t>
+          <t>Initial state transitions to Off.</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Off state is present</t>
+          <t>Off state is present.</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Transition masterOn from Off to On is present</t>
+          <t>Transition from Off to On is present.</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>On is a composite state containing substates</t>
+          <t>On is a composite state.</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Transition masterOff from On to Off is present</t>
+          <t>Transition from On to Off is present.</t>
         </is>
       </c>
     </row>
@@ -5878,7 +5878,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Initial state in On correctly transitions to LoggedOut (equivalent to Idle)</t>
+          <t>Initial state inside On transitions to LoggedOut which serves the purpose of the ground truth Idle state.</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>LoggedOut state represents the idle/logged-out state</t>
+          <t>LoggedOut state represents the system waiting for login.</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Transition tapCard with unauthorized guard loops back to LoggedOut</t>
+          <t>Transition for failed login is present.</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Guard !authorized(cardId) is semantically equivalent</t>
+          <t>Guard for unauthorized card is present.</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Transition tapCard with authorized guard goes to UserSession (Ready equivalent)</t>
+          <t>Transition for successful login is present.</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Guard authorized(cardId) is present</t>
+          <t>Guard for authorized card is present.</t>
         </is>
       </c>
     </row>
@@ -5994,11 +5994,11 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>No action setting a variable to track mode is present</t>
+          <t>Student uses separate states instead of an action variable which is a valid alternative modeling approach.</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>UserSession with TaskSelection represents the ready state</t>
+          <t>Ready state is represented by Idle PrintReady and ScanReady states.</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Transition logoff from TaskSelection to LoggedOut is present</t>
+          <t>Logoff transitions are present from the ready states to LoggedOut.</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Self-transition on PrintChosen with !hasQueuedDocument guard shows error</t>
+          <t>Transition for scan start error is present.</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Guard !originalDetected() on ScanChosen self-transition is equivalent</t>
+          <t>Guard for missing document is present.</t>
         </is>
       </c>
       <c r="E17" s="4" t="n"/>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Self-transition on PrintChosen with !hasQueuedDocument guard is present</t>
+          <t>Transition for print start error is present.</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Guard !hasQueuedDocument() is semantically equivalent</t>
+          <t>Guard for empty queue is present.</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Transition chooseScan within TaskSelection changes option</t>
+          <t>Transitions to choose scan mode are present.</t>
         </is>
       </c>
     </row>
@@ -6172,11 +6172,11 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>No explicit action variable assignment for scan mode</t>
+          <t>Modeled using state change to ScanReady instead of an action variable.</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Transition choosePrint within TaskSelection changes option</t>
+          <t>Transitions to choose print mode are present.</t>
         </is>
       </c>
     </row>
@@ -6212,11 +6212,11 @@
         </is>
       </c>
       <c r="C23" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>No explicit action variable assignment for print mode</t>
+          <t>Modeled using state change to PrintReady instead of an action variable.</t>
         </is>
       </c>
       <c r="E23" s="4" t="n"/>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Transition from ScanChosen to Scanning with originalDetected guard is present</t>
+          <t>Transition to start scanning is present.</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Guard originalDetected() on ScanChosen to Scanning transition is equivalent</t>
+          <t>Guard for document detected is present.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>ActiveTask composite state represents the busy state</t>
+          <t>Busy state behavior is correctly represented by separate Printing and Scanning states with their respective transitions.</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Transition pressStop from ActiveTask to TaskSelection is present</t>
+          <t>Stop transitions are present from both printing and scanning states.</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Transitions printDone and scanDone from Printing/Scanning to TaskSelection are present</t>
+          <t>Done transitions are present from both printing and scanning states.</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Transition paperJam from ActiveTask to PaperJamRecovery is present</t>
+          <t>Jam transitions are present for both printing and scanning.</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>History state H is present in ActiveTask</t>
+          <t>Student explicitly models resume transitions to the specific active states instead of using a history state.</t>
         </is>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Printing state is present</t>
+          <t>Printing state is present.</t>
         </is>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Transition from PrintChosen to Printing with hasQueuedDocument guard is present</t>
+          <t>Transition to start printing is present.</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Guard hasQueuedDocument() is semantically equivalent</t>
+          <t>Guard for non-empty queue is present.</t>
         </is>
       </c>
     </row>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Transition outOfPaper from Printing to OutOfPaperRecovery is present</t>
+          <t>Out of paper transition is present.</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Scanning state represents scan and email functionality</t>
+          <t>Scanning state is present.</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>PaperJamRecovery and OutOfPaperRecovery represent suspended states</t>
+          <t>Suspended states are explicitly modeled for each condition.</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Transitions resume from recovery states to history state H are present</t>
+          <t>Resume transitions correctly return to the specific interrupted states.</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Transitions cancel from recovery states to TaskSelection are present</t>
+          <t>Cancel transitions correctly return to the respective ready states.</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect states present</t>
+          <t>Extra states are reasonable modeling choices for the chosen architecture.</t>
         </is>
       </c>
       <c r="E39" s="4" t="n"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect transitions present</t>
+          <t>Extra transitions are necessary for the state-based approach and do not violate system behavior.</t>
         </is>
       </c>
       <c r="E40" s="4" t="n"/>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect guards present</t>
+          <t>No incorrect additional guards.</t>
         </is>
       </c>
       <c r="E41" s="4" t="n"/>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect actions present</t>
+          <t>Additional actions correctly reflect the system description.</t>
         </is>
       </c>
       <c r="E42" s="4" t="n"/>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Additional composite states are reasonable modeling choices</t>
+          <t>LoggedIn composite state is a reasonable modeling choice.</t>
         </is>
       </c>
       <c r="E43" s="4" t="n"/>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>No incorrect regions present</t>
+          <t>No additional regions.</t>
         </is>
       </c>
       <c r="E44" s="4" t="n"/>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>No incorrect history states present</t>
+          <t>No additional history states.</t>
         </is>
       </c>
       <c r="E45" s="4" t="n"/>
@@ -10726,7 +10726,7 @@
     <row r="1" ht="15.75" customHeight="1" s="62">
       <c r="A1" s="67" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="14" t="inlineStr">
@@ -10793,15 +10793,15 @@
         <v/>
       </c>
       <c r="C3" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A3, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D3" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A3, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A3, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E3" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A3, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F3" s="18">
@@ -10828,15 +10828,15 @@
         <v/>
       </c>
       <c r="C4" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A4, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D4" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A4, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A4, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E4" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A4, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F4" s="18">
@@ -10868,15 +10868,15 @@
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A5, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A5, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A5, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A5, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F5" s="18">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -10908,15 +10908,15 @@
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A6, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A6, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A6, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A6, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F6" s="18">
@@ -10943,15 +10943,15 @@
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A7, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A7, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A7, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E7" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A7, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F7" s="18">
@@ -10983,15 +10983,15 @@
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A8, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A8, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A8, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E8" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A8, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F8" s="18">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="J8" s="60" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -11023,15 +11023,15 @@
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$38, $A9, 'GPT-5 Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>SUMIF('GPT-5 Generation'!$A$39:$A$45, $A9, 'GPT-5 Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A9, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$38, $A9, 'GPT-5 Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F9" s="18">

--- a/Printer/Grading/2 stage/6-examples/Printer_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Printer/Grading/2 stage/6-examples/Printer_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="printer" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gemini 3.1 Pro Grading" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -10793,15 +10793,15 @@
         <v/>
       </c>
       <c r="C3" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D3" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A3, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A3, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E3" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F3" s="18">
@@ -10828,15 +10828,15 @@
         <v/>
       </c>
       <c r="C4" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D4" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A4, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A4, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E4" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F4" s="18">
@@ -10868,15 +10868,15 @@
         <v/>
       </c>
       <c r="C5" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A5, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A5, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F5" s="18">
@@ -10908,15 +10908,15 @@
         <v/>
       </c>
       <c r="C6" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A6, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A6, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F6" s="18">
@@ -10943,15 +10943,15 @@
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A7, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A7, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E7" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F7" s="18">
@@ -10983,15 +10983,15 @@
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A8, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A8, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E8" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F8" s="18">
@@ -11023,15 +11023,15 @@
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$38)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$38)</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$39:$A$45, $A9, 'Gemini 3.1 Pro Generation'!$C$39:$C$45)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$39:$A$45, $A9, 'Gemini 3.1 Pro Grading'!$C$39:$C$45)</f>
         <v/>
       </c>
       <c r="E9" s="18">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$38, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$38,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$38, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$38,0)</f>
         <v/>
       </c>
       <c r="F9" s="18">
